--- a/experiments/results/resnet18/CIFAR-10/ReAct/standard/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-10/ReAct/standard/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -666,6 +666,55 @@
       <c r="O6" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=0.4,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>94.12</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>96.37</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>93.69</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>29.76</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>95.19</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.5,scale_th=None,type=avg</t>
         </is>
       </c>
     </row>
